--- a/OUTPUT/direct_P0A4U6_Nostoc_sp__PCC_7120.xlsx
+++ b/OUTPUT/direct_P0A4U6_Nostoc_sp__PCC_7120.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.024</v>
+        <v>0.02419032387045182</v>
       </c>
     </row>
   </sheetData>
